--- a/survey_templates/041_cupping_knowledge_quiz--survey_templates.xlsx
+++ b/survey_templates/041_cupping_knowledge_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1091,17 +1091,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>contraindications_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pregnancy_or_breast-feeding</t>
+          <t>relaxation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pregnancy or breast-feeding</t>
+          <t>Relaxation</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>relaxation</t>
+          <t>pain_relief</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Relaxation</t>
+          <t>Pain relief</t>
         </is>
       </c>
     </row>
@@ -1130,29 +1130,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pain_relief</t>
+          <t>improved_sleep_quality</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pain relief</t>
+          <t>Improved sleep quality</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>benefits_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>improved_sleep_quality</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Improved sleep quality</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>diabetes</t>
+          <t>arthritis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Arthritis</t>
         </is>
       </c>
     </row>
@@ -1181,29 +1181,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>arthritis</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arthritis</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>cupping_certification_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>level_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Level 1</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>level_1</t>
+          <t>level_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
     </row>
@@ -1232,29 +1232,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>level_2</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cupping_certification_choices</t>
+          <t>cupping_course_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>level_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Level 1</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>level_1</t>
+          <t>level_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
     </row>
@@ -1283,29 +1283,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>level_2</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cupping_course_choices</t>
+          <t>how_often_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1334,29 +1334,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>how_often_choices</t>
+          <t>cupping_frequency_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1385,29 +1385,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cupping_frequency_choices</t>
+          <t>cupping_duration_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>5-15_min</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>5-15 min</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5-15_min</t>
+          <t>15-30_min</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5-15 min</t>
+          <t>15-30 min</t>
         </is>
       </c>
     </row>
@@ -1436,29 +1436,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15-30_min</t>
+          <t>30_min_or_more</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15-30 min</t>
+          <t>30 min or more</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cupping_duration_choices</t>
+          <t>cupping_area_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30_min_or_more</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>30 min or more</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>legs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Legs</t>
         </is>
       </c>
     </row>
@@ -1487,29 +1487,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>legs</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Legs</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cupping_area_choices</t>
+          <t>how_long_do_you_practice_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>less_than_1_year</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Less than 1 year</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1538,27 +1538,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1-2_years</t>
+          <t>more_than_2_years</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>1-2 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>how_long_do_you_practice_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>more_than_2_years</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>More than 2 years</t>
         </is>
